--- a/data/trans_camb/IP16B05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B05-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,31</t>
+          <t>0,0; 79,7</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,31</t>
+          <t>0,0; 79,7</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 14,49</t>
+          <t>-29,98; 14,19</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,98</t>
+          <t>0,0; 36,27</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 151,93</t>
+          <t>0,0; 392,67</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 151,93</t>
+          <t>0,0; 392,67</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 16,85</t>
+          <t>-33,21; 16,54</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,19</t>
+          <t>0,0; 56,92</t>
         </is>
       </c>
     </row>
@@ -1879,17 +1879,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 24,09</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,44</t>
+          <t>0,0; 28,67</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 0,0</t>
+          <t>-15,28; 0,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 9,95</t>
+          <t>-2,25; 10,6</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,54</t>
+          <t>0,0; 10,81</t>
         </is>
       </c>
     </row>
@@ -1955,17 +1955,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,17</t>
+          <t>0,0; 31,74</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,74</t>
+          <t>0,0; 40,29</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 0,0</t>
+          <t>-15,28; 0,0</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 11,04</t>
+          <t>-2,25; 11,94</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,34</t>
+          <t>0,0; 12,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B05-Provincia-trans_camb.xlsx
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,7</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,7</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 14,19</t>
+          <t>-26,92; 14,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,27</t>
+          <t>0,0; 34,25</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 392,67</t>
+          <t>0,0; 400,0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 392,67</t>
+          <t>0,0; 400,0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 16,54</t>
+          <t>-27,27; 16,74</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,92</t>
+          <t>0,0; 52,16</t>
         </is>
       </c>
     </row>
@@ -1879,17 +1879,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,09</t>
+          <t>0,0; 25,52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,67</t>
+          <t>0,0; 30,25</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 0,0</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,6</t>
+          <t>-2,93; 9,79</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,81</t>
+          <t>0,0; 13,66</t>
         </is>
       </c>
     </row>
@@ -1955,17 +1955,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,74</t>
+          <t>0,0; 34,41</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,29</t>
+          <t>0,0; 43,37</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 0,0</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 11,94</t>
+          <t>-2,93; 10,74</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,13</t>
+          <t>0,0; 15,84</t>
         </is>
       </c>
     </row>
